--- a/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
+++ b/KURIKULUM2026_REVISI/017_AUDIT_FORENSIK_ZERO_REDUNDANCY_DAN_ZERO_GAP.xlsx
@@ -613,7 +613,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>**`STI-413 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-626 Deep Learning`** (Sem 6)</t>
+          <t>**`STI-413 Machine Learning`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-726 Deep Learning`** (Sem 6)</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>**`STI-413`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-626`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
+          <t>**`STI-413`** fokus pada **Tabular &amp; Classical ML**: Scikit-Learn, Feature Engineering, SVM, Random Forest, K-Means, XGBoost.&lt;br&gt;**`STI-726`** fokus murni pada **Deep Representations &amp; Unstructured Data**: PyTorch/TensorFlow, Backpropagation, CNN (Vision), RNN/LSTM (Sequential), Attention Mechanism/Transformer.</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>**`STI-311 Web Front End`** (Sem 3)&lt;br&gt;vs&lt;br&gt;**`STI-416 Web Back End`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-627 Digital Platform Eng.`** (Sem 6)</t>
+          <t>**`STI-311 Web Front End`** (Sem 3)&lt;br&gt;vs&lt;br&gt;**`STI-416 Web Back End`** (Sem 4)&lt;br&gt;vs&lt;br&gt;**`STI-727 Digital Platform Eng.`** (Sem 6)</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>**`STI-311`** (Client-Side): HTML5, CSS Modern, JavaScript ES6+, React/Vue, DOM Manipulation, Responsive UI.&lt;br&gt;**`STI-416`** (Server-Side): RESTful API, NodeJS/Go/Python, JWT Authentication, ORM, Database Transactions, Redis Caching.&lt;br&gt;**`STI-627`** (Distributed Systems): Event-Driven Architecture, Message Broker (RabbitMQ/Kafka), API Gateway, Docker Containerization, CI/CD Pipeline.</t>
+          <t>**`STI-311`** (Client-Side): HTML5, CSS Modern, JavaScript ES6+, React/Vue, DOM Manipulation, Responsive UI.&lt;br&gt;**`STI-416`** (Server-Side): RESTful API, NodeJS/Go/Python, JWT Authentication, ORM, Database Transactions, Redis Caching.&lt;br&gt;**`STI-727`** (Distributed Systems): Event-Driven Architecture, Message Broker (RabbitMQ/Kafka), API Gateway, Docker Containerization, CI/CD Pipeline.</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
